--- a/static/data/exports/Retro_PY_AE_2011.xlsx
+++ b/static/data/exports/Retro_PY_AE_2011.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Retro Data" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Retro Data" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -576,6 +576,19 @@
           <t>AINRC</t>
         </is>
       </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P2" t="n">
+        <v>39</v>
+      </c>
       <c r="Q2" t="b">
         <v>0</v>
       </c>
@@ -638,6 +651,19 @@
           <t>PMK</t>
         </is>
       </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P3" t="n">
+        <v>35</v>
+      </c>
       <c r="Q3" t="b">
         <v>0</v>
       </c>
@@ -700,6 +726,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P4" t="n">
+        <v>72</v>
+      </c>
       <c r="Q4" t="b">
         <v>0</v>
       </c>
@@ -762,6 +801,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P5" t="n">
+        <v>33</v>
+      </c>
       <c r="Q5" t="b">
         <v>0</v>
       </c>
@@ -824,6 +876,19 @@
           <t>BJP</t>
         </is>
       </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P6" t="n">
+        <v>57</v>
+      </c>
       <c r="Q6" t="b">
         <v>0</v>
       </c>
@@ -886,6 +951,19 @@
           <t>JD(U)</t>
         </is>
       </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P7" t="n">
+        <v>31</v>
+      </c>
       <c r="Q7" t="b">
         <v>0</v>
       </c>
@@ -948,6 +1026,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P8" t="n">
+        <v>35</v>
+      </c>
       <c r="Q8" t="b">
         <v>0</v>
       </c>
@@ -1010,6 +1101,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P9" t="n">
+        <v>39</v>
+      </c>
       <c r="Q9" t="b">
         <v>0</v>
       </c>
@@ -1072,6 +1176,19 @@
           <t>AINRC</t>
         </is>
       </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P10" t="n">
+        <v>43</v>
+      </c>
       <c r="Q10" t="b">
         <v>0</v>
       </c>
@@ -1134,6 +1251,19 @@
           <t>INC</t>
         </is>
       </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P11" t="n">
+        <v>60</v>
+      </c>
       <c r="Q11" t="b">
         <v>0</v>
       </c>
@@ -1196,6 +1326,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P12" t="n">
+        <v>45</v>
+      </c>
       <c r="Q12" t="b">
         <v>0</v>
       </c>
@@ -1258,6 +1401,19 @@
           <t>BJP</t>
         </is>
       </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P13" t="n">
+        <v>43</v>
+      </c>
       <c r="Q13" t="b">
         <v>0</v>
       </c>
@@ -1320,6 +1476,19 @@
           <t>BSP</t>
         </is>
       </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P14" t="n">
+        <v>27</v>
+      </c>
       <c r="Q14" t="b">
         <v>0</v>
       </c>
@@ -1382,6 +1551,19 @@
           <t>AINRC</t>
         </is>
       </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P15" t="n">
+        <v>35</v>
+      </c>
       <c r="Q15" t="b">
         <v>0</v>
       </c>
@@ -1444,6 +1626,19 @@
           <t>DMK</t>
         </is>
       </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P16" t="n">
+        <v>46</v>
+      </c>
       <c r="Q16" t="b">
         <v>0</v>
       </c>
@@ -1506,6 +1701,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P17" t="n">
+        <v>53</v>
+      </c>
       <c r="Q17" t="b">
         <v>0</v>
       </c>
@@ -1568,6 +1776,19 @@
           <t>LJP</t>
         </is>
       </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P18" t="n">
+        <v>51</v>
+      </c>
       <c r="Q18" t="b">
         <v>0</v>
       </c>
@@ -1630,6 +1851,19 @@
           <t>PB</t>
         </is>
       </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P19" t="n">
+        <v>38</v>
+      </c>
       <c r="Q19" t="b">
         <v>0</v>
       </c>
@@ -1692,6 +1926,19 @@
           <t>BSP</t>
         </is>
       </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="P20" t="n">
+        <v>34</v>
+      </c>
       <c r="Q20" t="b">
         <v>0</v>
       </c>
@@ -1754,6 +2001,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P21" t="n">
+        <v>31</v>
+      </c>
       <c r="Q21" t="b">
         <v>0</v>
       </c>
@@ -1816,6 +2076,19 @@
           <t>INC</t>
         </is>
       </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P22" t="n">
+        <v>57</v>
+      </c>
       <c r="Q22" t="b">
         <v>0</v>
       </c>
@@ -1878,6 +2151,19 @@
           <t>AINRC</t>
         </is>
       </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P23" t="n">
+        <v>63</v>
+      </c>
       <c r="Q23" t="b">
         <v>0</v>
       </c>
@@ -1940,6 +2226,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P24" t="n">
+        <v>25</v>
+      </c>
       <c r="Q24" t="b">
         <v>0</v>
       </c>
@@ -2002,6 +2301,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P25" t="n">
+        <v>32</v>
+      </c>
       <c r="Q25" t="b">
         <v>0</v>
       </c>
@@ -2064,6 +2376,19 @@
           <t>BJP</t>
         </is>
       </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P26" t="n">
+        <v>44</v>
+      </c>
       <c r="Q26" t="b">
         <v>0</v>
       </c>
@@ -2126,6 +2451,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P27" t="n">
+        <v>50</v>
+      </c>
       <c r="Q27" t="b">
         <v>0</v>
       </c>
@@ -2188,6 +2526,19 @@
           <t>LJP</t>
         </is>
       </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P28" t="n">
+        <v>40</v>
+      </c>
       <c r="Q28" t="b">
         <v>0</v>
       </c>
@@ -2250,6 +2601,19 @@
           <t>IJK</t>
         </is>
       </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O29" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P29" t="n">
+        <v>46</v>
+      </c>
       <c r="Q29" t="b">
         <v>0</v>
       </c>
@@ -2312,6 +2676,19 @@
           <t>JD(U)</t>
         </is>
       </c>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O30" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P30" t="n">
+        <v>31</v>
+      </c>
       <c r="Q30" t="b">
         <v>0</v>
       </c>
@@ -2374,6 +2751,19 @@
           <t>INC</t>
         </is>
       </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O31" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P31" t="n">
+        <v>41</v>
+      </c>
       <c r="Q31" t="b">
         <v>0</v>
       </c>
@@ -2436,6 +2826,19 @@
           <t>AINRC</t>
         </is>
       </c>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O32" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P32" t="n">
+        <v>61</v>
+      </c>
       <c r="Q32" t="b">
         <v>0</v>
       </c>
@@ -2498,6 +2901,19 @@
           <t>BJP</t>
         </is>
       </c>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O33" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P33" t="n">
+        <v>51</v>
+      </c>
       <c r="Q33" t="b">
         <v>0</v>
       </c>
@@ -2560,6 +2976,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O34" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P34" t="n">
+        <v>32</v>
+      </c>
       <c r="Q34" t="b">
         <v>0</v>
       </c>
@@ -2622,6 +3051,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O35" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P35" t="n">
+        <v>30</v>
+      </c>
       <c r="Q35" t="b">
         <v>0</v>
       </c>
@@ -2684,6 +3126,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O36" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P36" t="n">
+        <v>27</v>
+      </c>
       <c r="Q36" t="b">
         <v>0</v>
       </c>
@@ -2746,6 +3201,19 @@
           <t>AINRC</t>
         </is>
       </c>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O37" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P37" t="n">
+        <v>48</v>
+      </c>
       <c r="Q37" t="b">
         <v>0</v>
       </c>
@@ -2808,6 +3276,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P38" t="n">
+        <v>46</v>
+      </c>
       <c r="Q38" t="b">
         <v>0</v>
       </c>
@@ -2870,6 +3351,19 @@
           <t>DMK</t>
         </is>
       </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P39" t="n">
+        <v>45</v>
+      </c>
       <c r="Q39" t="b">
         <v>0</v>
       </c>
@@ -2932,6 +3426,19 @@
           <t>BJP</t>
         </is>
       </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="P40" t="n">
+        <v>45</v>
+      </c>
       <c r="Q40" t="b">
         <v>0</v>
       </c>
@@ -2994,6 +3501,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P41" t="n">
+        <v>41</v>
+      </c>
       <c r="Q41" t="b">
         <v>0</v>
       </c>
@@ -3056,6 +3576,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P42" t="n">
+        <v>34</v>
+      </c>
       <c r="Q42" t="b">
         <v>0</v>
       </c>
@@ -3118,6 +3651,19 @@
           <t>IJK</t>
         </is>
       </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P43" t="n">
+        <v>37</v>
+      </c>
       <c r="Q43" t="b">
         <v>0</v>
       </c>
@@ -3180,6 +3726,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P44" t="n">
+        <v>26</v>
+      </c>
       <c r="Q44" t="b">
         <v>0</v>
       </c>
@@ -3242,6 +3801,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P45" t="n">
+        <v>35</v>
+      </c>
       <c r="Q45" t="b">
         <v>0</v>
       </c>
@@ -3304,6 +3876,19 @@
           <t>AINRC</t>
         </is>
       </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P46" t="n">
+        <v>61</v>
+      </c>
       <c r="Q46" t="b">
         <v>0</v>
       </c>
@@ -3366,6 +3951,19 @@
           <t>INC</t>
         </is>
       </c>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O47" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P47" t="n">
+        <v>63</v>
+      </c>
       <c r="Q47" t="b">
         <v>0</v>
       </c>
@@ -3428,6 +4026,19 @@
           <t>BJP</t>
         </is>
       </c>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O48" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="P48" t="n">
+        <v>41</v>
+      </c>
       <c r="Q48" t="b">
         <v>0</v>
       </c>
@@ -3490,6 +4101,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="O49" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P49" t="n">
+        <v>35</v>
+      </c>
       <c r="Q49" t="b">
         <v>0</v>
       </c>
@@ -3552,6 +4176,19 @@
           <t>AINRC</t>
         </is>
       </c>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O50" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P50" t="n">
+        <v>61</v>
+      </c>
       <c r="Q50" t="b">
         <v>0</v>
       </c>
@@ -3614,6 +4251,19 @@
           <t>INC</t>
         </is>
       </c>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O51" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P51" t="n">
+        <v>47</v>
+      </c>
       <c r="Q51" t="b">
         <v>0</v>
       </c>
@@ -3676,6 +4326,19 @@
           <t>AINRC</t>
         </is>
       </c>
+      <c r="N52" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O52" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P52" t="n">
+        <v>36</v>
+      </c>
       <c r="Q52" t="b">
         <v>0</v>
       </c>
@@ -3738,6 +4401,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O53" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P53" t="n">
+        <v>65</v>
+      </c>
       <c r="Q53" t="b">
         <v>0</v>
       </c>
@@ -3800,6 +4476,19 @@
           <t>DMK</t>
         </is>
       </c>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O54" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P54" t="n">
+        <v>39</v>
+      </c>
       <c r="Q54" t="b">
         <v>0</v>
       </c>
@@ -3862,6 +4551,19 @@
           <t>BJP</t>
         </is>
       </c>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O55" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P55" t="n">
+        <v>34</v>
+      </c>
       <c r="Q55" t="b">
         <v>0</v>
       </c>
@@ -3924,6 +4626,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N56" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O56" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P56" t="n">
+        <v>44</v>
+      </c>
       <c r="Q56" t="b">
         <v>0</v>
       </c>
@@ -3986,6 +4701,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N57" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O57" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P57" t="n">
+        <v>36</v>
+      </c>
       <c r="Q57" t="b">
         <v>0</v>
       </c>
@@ -4048,6 +4776,19 @@
           <t>BSP</t>
         </is>
       </c>
+      <c r="N58" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O58" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P58" t="n">
+        <v>29</v>
+      </c>
       <c r="Q58" t="b">
         <v>0</v>
       </c>
@@ -4110,6 +4851,19 @@
           <t>INC</t>
         </is>
       </c>
+      <c r="N59" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O59" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P59" t="n">
+        <v>60</v>
+      </c>
       <c r="Q59" t="b">
         <v>0</v>
       </c>
@@ -4172,6 +4926,19 @@
           <t>CPI</t>
         </is>
       </c>
+      <c r="N60" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O60" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P60" t="n">
+        <v>51</v>
+      </c>
       <c r="Q60" t="b">
         <v>0</v>
       </c>
@@ -4234,6 +5001,19 @@
           <t>BJP</t>
         </is>
       </c>
+      <c r="N61" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O61" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P61" t="n">
+        <v>46</v>
+      </c>
       <c r="Q61" t="b">
         <v>0</v>
       </c>
@@ -4296,6 +5076,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N62" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O62" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P62" t="n">
+        <v>39</v>
+      </c>
       <c r="Q62" t="b">
         <v>0</v>
       </c>
@@ -4358,6 +5151,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N63" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O63" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P63" t="n">
+        <v>38</v>
+      </c>
       <c r="Q63" t="b">
         <v>0</v>
       </c>
@@ -4420,6 +5226,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N64" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="O64" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P64" t="n">
+        <v>27</v>
+      </c>
       <c r="Q64" t="b">
         <v>0</v>
       </c>
@@ -4482,6 +5301,19 @@
           <t>BSP</t>
         </is>
       </c>
+      <c r="N65" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O65" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P65" t="n">
+        <v>31</v>
+      </c>
       <c r="Q65" t="b">
         <v>0</v>
       </c>
@@ -4544,6 +5376,19 @@
           <t>LJP</t>
         </is>
       </c>
+      <c r="N66" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O66" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P66" t="n">
+        <v>28</v>
+      </c>
       <c r="Q66" t="b">
         <v>0</v>
       </c>
@@ -4606,6 +5451,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N67" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O67" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P67" t="n">
+        <v>26</v>
+      </c>
       <c r="Q67" t="b">
         <v>0</v>
       </c>
@@ -4668,6 +5526,19 @@
           <t>AINRC</t>
         </is>
       </c>
+      <c r="N68" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O68" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P68" t="n">
+        <v>37</v>
+      </c>
       <c r="Q68" t="b">
         <v>0</v>
       </c>
@@ -4730,6 +5601,19 @@
           <t>INC</t>
         </is>
       </c>
+      <c r="N69" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O69" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P69" t="n">
+        <v>59</v>
+      </c>
       <c r="Q69" t="b">
         <v>0</v>
       </c>
@@ -4792,6 +5676,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N70" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O70" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P70" t="n">
+        <v>40</v>
+      </c>
       <c r="Q70" t="b">
         <v>0</v>
       </c>
@@ -4854,6 +5751,19 @@
           <t>BJP</t>
         </is>
       </c>
+      <c r="N71" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O71" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P71" t="n">
+        <v>42</v>
+      </c>
       <c r="Q71" t="b">
         <v>0</v>
       </c>
@@ -4916,6 +5826,19 @@
           <t>CPM</t>
         </is>
       </c>
+      <c r="N72" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O72" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P72" t="n">
+        <v>62</v>
+      </c>
       <c r="Q72" t="b">
         <v>0</v>
       </c>
@@ -4978,6 +5901,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N73" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O73" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P73" t="n">
+        <v>43</v>
+      </c>
       <c r="Q73" t="b">
         <v>0</v>
       </c>
@@ -5040,6 +5976,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N74" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O74" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P74" t="n">
+        <v>37</v>
+      </c>
       <c r="Q74" t="b">
         <v>0</v>
       </c>
@@ -5102,6 +6051,19 @@
           <t>AINRC</t>
         </is>
       </c>
+      <c r="N75" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O75" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P75" t="n">
+        <v>33</v>
+      </c>
       <c r="Q75" t="b">
         <v>0</v>
       </c>
@@ -5164,6 +6126,19 @@
           <t>INC</t>
         </is>
       </c>
+      <c r="N76" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O76" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P76" t="n">
+        <v>46</v>
+      </c>
       <c r="Q76" t="b">
         <v>0</v>
       </c>
@@ -5226,6 +6201,19 @@
           <t>BJP</t>
         </is>
       </c>
+      <c r="N77" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O77" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P77" t="n">
+        <v>41</v>
+      </c>
       <c r="Q77" t="b">
         <v>0</v>
       </c>
@@ -5288,6 +6276,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N78" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O78" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P78" t="n">
+        <v>55</v>
+      </c>
       <c r="Q78" t="b">
         <v>0</v>
       </c>
@@ -5350,6 +6351,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N79" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O79" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P79" t="n">
+        <v>28</v>
+      </c>
       <c r="Q79" t="b">
         <v>0</v>
       </c>
@@ -5412,6 +6426,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N80" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O80" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P80" t="n">
+        <v>26</v>
+      </c>
       <c r="Q80" t="b">
         <v>0</v>
       </c>
@@ -5474,6 +6501,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N81" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O81" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P81" t="n">
+        <v>45</v>
+      </c>
       <c r="Q81" t="b">
         <v>0</v>
       </c>
@@ -5536,6 +6576,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N82" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O82" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P82" t="n">
+        <v>50</v>
+      </c>
       <c r="Q82" t="b">
         <v>0</v>
       </c>
@@ -5598,6 +6651,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N83" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="O83" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P83" t="n">
+        <v>37</v>
+      </c>
       <c r="Q83" t="b">
         <v>0</v>
       </c>
@@ -5660,6 +6726,19 @@
           <t>DMK</t>
         </is>
       </c>
+      <c r="N84" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O84" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P84" t="n">
+        <v>40</v>
+      </c>
       <c r="Q84" t="b">
         <v>0</v>
       </c>
@@ -5722,6 +6801,19 @@
           <t>AIADMK</t>
         </is>
       </c>
+      <c r="N85" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O85" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P85" t="n">
+        <v>79</v>
+      </c>
       <c r="Q85" t="b">
         <v>0</v>
       </c>
@@ -5784,6 +6876,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N86" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O86" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P86" t="n">
+        <v>53</v>
+      </c>
       <c r="Q86" t="b">
         <v>0</v>
       </c>
@@ -5846,6 +6951,19 @@
           <t>BJP</t>
         </is>
       </c>
+      <c r="N87" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O87" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P87" t="n">
+        <v>42</v>
+      </c>
       <c r="Q87" t="b">
         <v>0</v>
       </c>
@@ -5908,6 +7026,19 @@
           <t>CPI(ML)(L)</t>
         </is>
       </c>
+      <c r="N88" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O88" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P88" t="n">
+        <v>31</v>
+      </c>
       <c r="Q88" t="b">
         <v>0</v>
       </c>
@@ -5970,6 +7101,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N89" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O89" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P89" t="n">
+        <v>58</v>
+      </c>
       <c r="Q89" t="b">
         <v>0</v>
       </c>
@@ -6032,6 +7176,19 @@
           <t>INC</t>
         </is>
       </c>
+      <c r="N90" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O90" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P90" t="n">
+        <v>51</v>
+      </c>
       <c r="Q90" t="b">
         <v>0</v>
       </c>
@@ -6094,6 +7251,19 @@
           <t>AIADMK</t>
         </is>
       </c>
+      <c r="N91" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O91" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P91" t="n">
+        <v>41</v>
+      </c>
       <c r="Q91" t="b">
         <v>0</v>
       </c>
@@ -6156,6 +7326,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N92" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O92" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P92" t="n">
+        <v>45</v>
+      </c>
       <c r="Q92" t="b">
         <v>0</v>
       </c>
@@ -6218,6 +7401,19 @@
           <t>BJP</t>
         </is>
       </c>
+      <c r="N93" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O93" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P93" t="n">
+        <v>55</v>
+      </c>
       <c r="Q93" t="b">
         <v>0</v>
       </c>
@@ -6280,6 +7476,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N94" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O94" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P94" t="n">
+        <v>49</v>
+      </c>
       <c r="Q94" t="b">
         <v>0</v>
       </c>
@@ -6342,6 +7551,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N95" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O95" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P95" t="n">
+        <v>56</v>
+      </c>
       <c r="Q95" t="b">
         <v>0</v>
       </c>
@@ -6404,6 +7626,19 @@
           <t>AIADMK</t>
         </is>
       </c>
+      <c r="N96" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O96" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P96" t="n">
+        <v>54</v>
+      </c>
       <c r="Q96" t="b">
         <v>0</v>
       </c>
@@ -6466,6 +7701,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N97" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O97" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P97" t="n">
+        <v>48</v>
+      </c>
       <c r="Q97" t="b">
         <v>0</v>
       </c>
@@ -6528,6 +7776,19 @@
           <t>DMK</t>
         </is>
       </c>
+      <c r="N98" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O98" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P98" t="n">
+        <v>46</v>
+      </c>
       <c r="Q98" t="b">
         <v>0</v>
       </c>
@@ -6590,6 +7851,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N99" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O99" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P99" t="n">
+        <v>51</v>
+      </c>
       <c r="Q99" t="b">
         <v>0</v>
       </c>
@@ -6652,6 +7926,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N100" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O100" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P100" t="n">
+        <v>26</v>
+      </c>
       <c r="Q100" t="b">
         <v>0</v>
       </c>
@@ -6714,6 +8001,19 @@
           <t>BSP</t>
         </is>
       </c>
+      <c r="N101" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="O101" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P101" t="n">
+        <v>40</v>
+      </c>
       <c r="Q101" t="b">
         <v>0</v>
       </c>
@@ -6776,6 +8076,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N102" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O102" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P102" t="n">
+        <v>35</v>
+      </c>
       <c r="Q102" t="b">
         <v>0</v>
       </c>
@@ -6838,6 +8151,19 @@
           <t>LJP</t>
         </is>
       </c>
+      <c r="N103" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="O103" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P103" t="n">
+        <v>51</v>
+      </c>
       <c r="Q103" t="b">
         <v>0</v>
       </c>
@@ -6900,6 +8226,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N104" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O104" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P104" t="n">
+        <v>31</v>
+      </c>
       <c r="Q104" t="b">
         <v>0</v>
       </c>
@@ -6962,6 +8301,19 @@
           <t>AINRC</t>
         </is>
       </c>
+      <c r="N105" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O105" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P105" t="n">
+        <v>47</v>
+      </c>
       <c r="Q105" t="b">
         <v>0</v>
       </c>
@@ -7024,6 +8376,19 @@
           <t>DMK</t>
         </is>
       </c>
+      <c r="N106" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O106" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P106" t="n">
+        <v>43</v>
+      </c>
       <c r="Q106" t="b">
         <v>0</v>
       </c>
@@ -7086,6 +8451,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N107" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O107" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P107" t="n">
+        <v>27</v>
+      </c>
       <c r="Q107" t="b">
         <v>0</v>
       </c>
@@ -7148,6 +8526,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N108" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O108" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P108" t="n">
+        <v>54</v>
+      </c>
       <c r="Q108" t="b">
         <v>0</v>
       </c>
@@ -7210,6 +8601,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N109" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O109" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P109" t="n">
+        <v>50</v>
+      </c>
       <c r="Q109" t="b">
         <v>0</v>
       </c>
@@ -7272,6 +8676,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N110" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O110" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P110" t="n">
+        <v>51</v>
+      </c>
       <c r="Q110" t="b">
         <v>0</v>
       </c>
@@ -7334,6 +8751,19 @@
           <t>JD(U)</t>
         </is>
       </c>
+      <c r="N111" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O111" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P111" t="n">
+        <v>44</v>
+      </c>
       <c r="Q111" t="b">
         <v>0</v>
       </c>
@@ -7396,6 +8826,19 @@
           <t>BSP</t>
         </is>
       </c>
+      <c r="N112" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O112" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P112" t="n">
+        <v>42</v>
+      </c>
       <c r="Q112" t="b">
         <v>0</v>
       </c>
@@ -7458,6 +8901,19 @@
           <t>AIADMK</t>
         </is>
       </c>
+      <c r="N113" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O113" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P113" t="n">
+        <v>50</v>
+      </c>
       <c r="Q113" t="b">
         <v>0</v>
       </c>
@@ -7520,6 +8976,19 @@
           <t>DMK</t>
         </is>
       </c>
+      <c r="N114" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O114" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P114" t="n">
+        <v>70</v>
+      </c>
       <c r="Q114" t="b">
         <v>0</v>
       </c>
@@ -7582,6 +9051,19 @@
           <t>BJP</t>
         </is>
       </c>
+      <c r="N115" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O115" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P115" t="n">
+        <v>46</v>
+      </c>
       <c r="Q115" t="b">
         <v>0</v>
       </c>
@@ -7644,6 +9126,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N116" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O116" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P116" t="n">
+        <v>34</v>
+      </c>
       <c r="Q116" t="b">
         <v>0</v>
       </c>
@@ -7706,6 +9201,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N117" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O117" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P117" t="n">
+        <v>31</v>
+      </c>
       <c r="Q117" t="b">
         <v>0</v>
       </c>
@@ -7768,6 +9276,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N118" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O118" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P118" t="n">
+        <v>63</v>
+      </c>
       <c r="Q118" t="b">
         <v>0</v>
       </c>
@@ -7830,6 +9351,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N119" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O119" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P119" t="n">
+        <v>51</v>
+      </c>
       <c r="Q119" t="b">
         <v>0</v>
       </c>
@@ -7892,6 +9426,19 @@
           <t>AIADMK</t>
         </is>
       </c>
+      <c r="N120" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O120" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P120" t="n">
+        <v>40</v>
+      </c>
       <c r="Q120" t="b">
         <v>0</v>
       </c>
@@ -7954,6 +9501,19 @@
           <t>DMK</t>
         </is>
       </c>
+      <c r="N121" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O121" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P121" t="n">
+        <v>64</v>
+      </c>
       <c r="Q121" t="b">
         <v>0</v>
       </c>
@@ -8016,6 +9576,19 @@
           <t>BJP</t>
         </is>
       </c>
+      <c r="N122" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O122" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P122" t="n">
+        <v>56</v>
+      </c>
       <c r="Q122" t="b">
         <v>0</v>
       </c>
@@ -8078,6 +9651,19 @@
           <t>IJK</t>
         </is>
       </c>
+      <c r="N123" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O123" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P123" t="n">
+        <v>31</v>
+      </c>
       <c r="Q123" t="b">
         <v>0</v>
       </c>
@@ -8140,6 +9726,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N124" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O124" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P124" t="n">
+        <v>49</v>
+      </c>
       <c r="Q124" t="b">
         <v>0</v>
       </c>
@@ -8202,6 +9801,19 @@
           <t>RSP</t>
         </is>
       </c>
+      <c r="N125" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O125" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P125" t="n">
+        <v>53</v>
+      </c>
       <c r="Q125" t="b">
         <v>0</v>
       </c>
@@ -8264,6 +9876,19 @@
           <t>AINRC</t>
         </is>
       </c>
+      <c r="N126" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O126" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P126" t="n">
+        <v>67</v>
+      </c>
       <c r="Q126" t="b">
         <v>0</v>
       </c>
@@ -8326,6 +9951,19 @@
           <t>INC</t>
         </is>
       </c>
+      <c r="N127" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O127" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P127" t="n">
+        <v>52</v>
+      </c>
       <c r="Q127" t="b">
         <v>0</v>
       </c>
@@ -8388,6 +10026,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N128" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O128" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P128" t="n">
+        <v>42</v>
+      </c>
       <c r="Q128" t="b">
         <v>0</v>
       </c>
@@ -8450,6 +10101,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N129" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O129" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P129" t="n">
+        <v>61</v>
+      </c>
       <c r="Q129" t="b">
         <v>0</v>
       </c>
@@ -8512,6 +10176,19 @@
           <t>BJP</t>
         </is>
       </c>
+      <c r="N130" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O130" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P130" t="n">
+        <v>37</v>
+      </c>
       <c r="Q130" t="b">
         <v>0</v>
       </c>
@@ -8574,6 +10251,19 @@
           <t>IJK</t>
         </is>
       </c>
+      <c r="N131" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O131" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P131" t="n">
+        <v>34</v>
+      </c>
       <c r="Q131" t="b">
         <v>0</v>
       </c>
@@ -8636,6 +10326,19 @@
           <t>AIADMK</t>
         </is>
       </c>
+      <c r="N132" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O132" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P132" t="n">
+        <v>63</v>
+      </c>
       <c r="Q132" t="b">
         <v>0</v>
       </c>
@@ -8698,6 +10401,19 @@
           <t>PMK</t>
         </is>
       </c>
+      <c r="N133" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O133" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P133" t="n">
+        <v>38</v>
+      </c>
       <c r="Q133" t="b">
         <v>0</v>
       </c>
@@ -8760,6 +10476,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N134" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O134" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P134" t="n">
+        <v>49</v>
+      </c>
       <c r="Q134" t="b">
         <v>0</v>
       </c>
@@ -8822,6 +10551,19 @@
           <t>IJK</t>
         </is>
       </c>
+      <c r="N135" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O135" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P135" t="n">
+        <v>41</v>
+      </c>
       <c r="Q135" t="b">
         <v>0</v>
       </c>
@@ -8884,6 +10626,19 @@
           <t>AINRC</t>
         </is>
       </c>
+      <c r="N136" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="O136" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P136" t="n">
+        <v>49</v>
+      </c>
       <c r="Q136" t="b">
         <v>0</v>
       </c>
@@ -8946,6 +10701,19 @@
           <t>INC</t>
         </is>
       </c>
+      <c r="N137" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="O137" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P137" t="n">
+        <v>45</v>
+      </c>
       <c r="Q137" t="b">
         <v>0</v>
       </c>
@@ -9008,6 +10776,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N138" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="O138" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P138" t="n">
+        <v>46</v>
+      </c>
       <c r="Q138" t="b">
         <v>0</v>
       </c>
@@ -9070,6 +10851,19 @@
           <t>CPI(ML)(L)</t>
         </is>
       </c>
+      <c r="N139" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="O139" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P139" t="n">
+        <v>42</v>
+      </c>
       <c r="Q139" t="b">
         <v>0</v>
       </c>
@@ -9132,6 +10926,19 @@
           <t>AIADMK</t>
         </is>
       </c>
+      <c r="N140" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="O140" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P140" t="n">
+        <v>52</v>
+      </c>
       <c r="Q140" t="b">
         <v>0</v>
       </c>
@@ -9194,6 +11001,19 @@
           <t>INC</t>
         </is>
       </c>
+      <c r="N141" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="O141" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P141" t="n">
+        <v>34</v>
+      </c>
       <c r="Q141" t="b">
         <v>0</v>
       </c>
@@ -9256,6 +11076,19 @@
           <t>BJP</t>
         </is>
       </c>
+      <c r="N142" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="O142" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P142" t="n">
+        <v>34</v>
+      </c>
       <c r="Q142" t="b">
         <v>0</v>
       </c>
@@ -9318,6 +11151,19 @@
           <t>BSP</t>
         </is>
       </c>
+      <c r="N143" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="O143" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P143" t="n">
+        <v>52</v>
+      </c>
       <c r="Q143" t="b">
         <v>0</v>
       </c>
@@ -9380,6 +11226,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N144" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="O144" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P144" t="n">
+        <v>35</v>
+      </c>
       <c r="Q144" t="b">
         <v>0</v>
       </c>
@@ -9442,6 +11301,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N145" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="O145" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P145" t="n">
+        <v>34</v>
+      </c>
       <c r="Q145" t="b">
         <v>0</v>
       </c>
@@ -9504,6 +11376,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N146" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="O146" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P146" t="n">
+        <v>34</v>
+      </c>
       <c r="Q146" t="b">
         <v>0</v>
       </c>
@@ -9566,6 +11451,19 @@
           <t>AINRC</t>
         </is>
       </c>
+      <c r="N147" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O147" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P147" t="n">
+        <v>59</v>
+      </c>
       <c r="Q147" t="b">
         <v>0</v>
       </c>
@@ -9628,6 +11526,19 @@
           <t>INC</t>
         </is>
       </c>
+      <c r="N148" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O148" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P148" t="n">
+        <v>39</v>
+      </c>
       <c r="Q148" t="b">
         <v>0</v>
       </c>
@@ -9690,6 +11601,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N149" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O149" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P149" t="n">
+        <v>56</v>
+      </c>
       <c r="Q149" t="b">
         <v>0</v>
       </c>
@@ -9752,6 +11676,19 @@
           <t>BJP</t>
         </is>
       </c>
+      <c r="N150" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O150" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P150" t="n">
+        <v>31</v>
+      </c>
       <c r="Q150" t="b">
         <v>0</v>
       </c>
@@ -9814,6 +11751,19 @@
           <t>AINRC</t>
         </is>
       </c>
+      <c r="N151" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="O151" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P151" t="n">
+        <v>62</v>
+      </c>
       <c r="Q151" t="b">
         <v>0</v>
       </c>
@@ -9876,6 +11826,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N152" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="O152" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P152" t="n">
+        <v>69</v>
+      </c>
       <c r="Q152" t="b">
         <v>0</v>
       </c>
@@ -9938,6 +11901,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N153" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="O153" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P153" t="n">
+        <v>55</v>
+      </c>
       <c r="Q153" t="b">
         <v>0</v>
       </c>
@@ -10000,6 +11976,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N154" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="O154" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P154" t="n">
+        <v>29</v>
+      </c>
       <c r="Q154" t="b">
         <v>0</v>
       </c>
@@ -10062,6 +12051,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N155" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="O155" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P155" t="n">
+        <v>37</v>
+      </c>
       <c r="Q155" t="b">
         <v>0</v>
       </c>
@@ -10124,6 +12126,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N156" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="O156" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P156" t="n">
+        <v>44</v>
+      </c>
       <c r="Q156" t="b">
         <v>0</v>
       </c>
@@ -10186,6 +12201,19 @@
           <t>AINRC</t>
         </is>
       </c>
+      <c r="N157" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O157" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P157" t="n">
+        <v>35</v>
+      </c>
       <c r="Q157" t="b">
         <v>0</v>
       </c>
@@ -10248,6 +12276,19 @@
           <t>INC</t>
         </is>
       </c>
+      <c r="N158" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O158" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P158" t="n">
+        <v>53</v>
+      </c>
       <c r="Q158" t="b">
         <v>0</v>
       </c>
@@ -10310,6 +12351,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N159" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O159" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P159" t="n">
+        <v>34</v>
+      </c>
       <c r="Q159" t="b">
         <v>0</v>
       </c>
@@ -10372,6 +12426,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N160" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O160" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P160" t="n">
+        <v>38</v>
+      </c>
       <c r="Q160" t="b">
         <v>0</v>
       </c>
@@ -10434,6 +12501,19 @@
           <t>BSP</t>
         </is>
       </c>
+      <c r="N161" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="O161" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="P161" t="n">
+        <v>27</v>
+      </c>
       <c r="Q161" t="b">
         <v>0</v>
       </c>
@@ -10496,6 +12576,19 @@
           <t>INC</t>
         </is>
       </c>
+      <c r="N162" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O162" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P162" t="n">
+        <v>38</v>
+      </c>
       <c r="Q162" t="b">
         <v>0</v>
       </c>
@@ -10558,6 +12651,19 @@
           <t>AIADMK</t>
         </is>
       </c>
+      <c r="N163" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O163" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P163" t="n">
+        <v>39</v>
+      </c>
       <c r="Q163" t="b">
         <v>0</v>
       </c>
@@ -10620,6 +12726,19 @@
           <t>BJP</t>
         </is>
       </c>
+      <c r="N164" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O164" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P164" t="n">
+        <v>45</v>
+      </c>
       <c r="Q164" t="b">
         <v>0</v>
       </c>
@@ -10682,6 +12801,19 @@
           <t>CPI(ML)(L)</t>
         </is>
       </c>
+      <c r="N165" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="O165" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P165" t="n">
+        <v>53</v>
+      </c>
       <c r="Q165" t="b">
         <v>0</v>
       </c>
@@ -10744,6 +12876,19 @@
           <t>DMK</t>
         </is>
       </c>
+      <c r="N166" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O166" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P166" t="n">
+        <v>49</v>
+      </c>
       <c r="Q166" t="b">
         <v>0</v>
       </c>
@@ -10806,6 +12951,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N167" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O167" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P167" t="n">
+        <v>50</v>
+      </c>
       <c r="Q167" t="b">
         <v>0</v>
       </c>
@@ -10868,6 +13026,19 @@
           <t>DMDK</t>
         </is>
       </c>
+      <c r="N168" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O168" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P168" t="n">
+        <v>57</v>
+      </c>
       <c r="Q168" t="b">
         <v>0</v>
       </c>
@@ -10930,6 +13101,19 @@
           <t>BSP</t>
         </is>
       </c>
+      <c r="N169" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O169" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P169" t="n">
+        <v>52</v>
+      </c>
       <c r="Q169" t="b">
         <v>0</v>
       </c>
@@ -10992,6 +13176,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N170" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O170" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P170" t="n">
+        <v>60</v>
+      </c>
       <c r="Q170" t="b">
         <v>0</v>
       </c>
@@ -11054,6 +13251,19 @@
           <t>DMK</t>
         </is>
       </c>
+      <c r="N171" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O171" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="P171" t="n">
+        <v>38</v>
+      </c>
       <c r="Q171" t="b">
         <v>0</v>
       </c>
@@ -11116,6 +13326,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N172" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O172" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P172" t="n">
+        <v>51</v>
+      </c>
       <c r="Q172" t="b">
         <v>0</v>
       </c>
@@ -11178,6 +13401,19 @@
           <t>AIADMK</t>
         </is>
       </c>
+      <c r="N173" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O173" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P173" t="n">
+        <v>65</v>
+      </c>
       <c r="Q173" t="b">
         <v>0</v>
       </c>
@@ -11240,6 +13476,19 @@
           <t>SDPI</t>
         </is>
       </c>
+      <c r="N174" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O174" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P174" t="n">
+        <v>38</v>
+      </c>
       <c r="Q174" t="b">
         <v>0</v>
       </c>
@@ -11302,6 +13551,19 @@
           <t>BSP</t>
         </is>
       </c>
+      <c r="N175" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O175" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P175" t="n">
+        <v>36</v>
+      </c>
       <c r="Q175" t="b">
         <v>0</v>
       </c>
@@ -11364,6 +13626,19 @@
           <t>INC</t>
         </is>
       </c>
+      <c r="N176" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O176" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P176" t="n">
+        <v>57</v>
+      </c>
       <c r="Q176" t="b">
         <v>0</v>
       </c>
@@ -11426,6 +13701,19 @@
           <t>CPM</t>
         </is>
       </c>
+      <c r="N177" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O177" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P177" t="n">
+        <v>64</v>
+      </c>
       <c r="Q177" t="b">
         <v>0</v>
       </c>
@@ -11488,6 +13776,19 @@
           <t>BJP</t>
         </is>
       </c>
+      <c r="N178" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O178" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P178" t="n">
+        <v>62</v>
+      </c>
       <c r="Q178" t="b">
         <v>0</v>
       </c>
@@ -11550,6 +13851,19 @@
           <t>INC</t>
         </is>
       </c>
+      <c r="N179" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O179" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P179" t="n">
+        <v>46</v>
+      </c>
       <c r="Q179" t="b">
         <v>0</v>
       </c>
@@ -11612,6 +13926,19 @@
           <t>AIADMK</t>
         </is>
       </c>
+      <c r="N180" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O180" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P180" t="n">
+        <v>45</v>
+      </c>
       <c r="Q180" t="b">
         <v>0</v>
       </c>
@@ -11674,6 +14001,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N181" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="O181" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P181" t="n">
+        <v>34</v>
+      </c>
       <c r="Q181" t="b">
         <v>0</v>
       </c>
@@ -11736,6 +14076,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N182" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O182" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P182" t="n">
+        <v>52</v>
+      </c>
       <c r="Q182" t="b">
         <v>0</v>
       </c>
@@ -11798,6 +14151,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N183" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="O183" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P183" t="n">
+        <v>34</v>
+      </c>
       <c r="Q183" t="b">
         <v>0</v>
       </c>
@@ -11860,6 +14226,19 @@
           <t>BJP</t>
         </is>
       </c>
+      <c r="N184" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O184" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P184" t="n">
+        <v>47</v>
+      </c>
       <c r="Q184" t="b">
         <v>0</v>
       </c>
@@ -11922,6 +14301,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N185" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O185" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P185" t="n">
+        <v>40</v>
+      </c>
       <c r="Q185" t="b">
         <v>0</v>
       </c>
@@ -11984,6 +14376,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N186" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O186" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P186" t="n">
+        <v>44</v>
+      </c>
       <c r="Q186" t="b">
         <v>0</v>
       </c>
@@ -12046,6 +14451,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N187" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O187" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="P187" t="n">
+        <v>43</v>
+      </c>
       <c r="Q187" t="b">
         <v>0</v>
       </c>
@@ -12107,6 +14525,19 @@
         <is>
           <t>IND</t>
         </is>
+      </c>
+      <c r="N188" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O188" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P188" t="n">
+        <v>34</v>
       </c>
       <c r="Q188" t="b">
         <v>0</v>

--- a/static/data/exports/Retro_PY_AE_2011.xlsx
+++ b/static/data/exports/Retro_PY_AE_2011.xlsx
@@ -583,7 +583,7 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P2" t="n">
@@ -658,7 +658,7 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P3" t="n">
@@ -733,7 +733,7 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P4" t="n">
@@ -808,7 +808,7 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P5" t="n">
@@ -883,7 +883,7 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P6" t="n">
@@ -958,7 +958,7 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P7" t="n">
@@ -1033,7 +1033,7 @@
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P8" t="n">
@@ -1108,7 +1108,7 @@
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P9" t="n">
@@ -1183,7 +1183,7 @@
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P10" t="n">
@@ -1258,7 +1258,7 @@
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P11" t="n">
@@ -1333,7 +1333,7 @@
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P12" t="n">
@@ -1408,7 +1408,7 @@
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P13" t="n">
@@ -1483,7 +1483,7 @@
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P14" t="n">
@@ -1558,7 +1558,7 @@
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P15" t="n">
@@ -1633,7 +1633,7 @@
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P16" t="n">
@@ -1708,7 +1708,7 @@
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P17" t="n">
@@ -1783,7 +1783,7 @@
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P18" t="n">
@@ -1858,7 +1858,7 @@
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P19" t="n">
@@ -1933,7 +1933,7 @@
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>FEMALE</t>
         </is>
       </c>
       <c r="P20" t="n">
@@ -2008,7 +2008,7 @@
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P21" t="n">
@@ -2083,7 +2083,7 @@
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P22" t="n">
@@ -2158,7 +2158,7 @@
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P23" t="n">
@@ -2233,7 +2233,7 @@
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P24" t="n">
@@ -2308,7 +2308,7 @@
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P25" t="n">
@@ -2383,7 +2383,7 @@
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P26" t="n">
@@ -2458,7 +2458,7 @@
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P27" t="n">
@@ -2533,7 +2533,7 @@
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P28" t="n">
@@ -2608,7 +2608,7 @@
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P29" t="n">
@@ -2683,7 +2683,7 @@
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P30" t="n">
@@ -2758,7 +2758,7 @@
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P31" t="n">
@@ -2833,7 +2833,7 @@
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P32" t="n">
@@ -2908,7 +2908,7 @@
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P33" t="n">
@@ -2983,7 +2983,7 @@
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P34" t="n">
@@ -3058,7 +3058,7 @@
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P35" t="n">
@@ -3133,7 +3133,7 @@
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P36" t="n">
@@ -3208,7 +3208,7 @@
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P37" t="n">
@@ -3283,7 +3283,7 @@
       </c>
       <c r="O38" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P38" t="n">
@@ -3358,7 +3358,7 @@
       </c>
       <c r="O39" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P39" t="n">
@@ -3433,7 +3433,7 @@
       </c>
       <c r="O40" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>FEMALE</t>
         </is>
       </c>
       <c r="P40" t="n">
@@ -3508,7 +3508,7 @@
       </c>
       <c r="O41" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P41" t="n">
@@ -3583,7 +3583,7 @@
       </c>
       <c r="O42" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P42" t="n">
@@ -3658,7 +3658,7 @@
       </c>
       <c r="O43" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P43" t="n">
@@ -3733,7 +3733,7 @@
       </c>
       <c r="O44" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P44" t="n">
@@ -3808,7 +3808,7 @@
       </c>
       <c r="O45" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P45" t="n">
@@ -3883,7 +3883,7 @@
       </c>
       <c r="O46" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P46" t="n">
@@ -3958,7 +3958,7 @@
       </c>
       <c r="O47" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P47" t="n">
@@ -4033,7 +4033,7 @@
       </c>
       <c r="O48" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>FEMALE</t>
         </is>
       </c>
       <c r="P48" t="n">
@@ -4108,7 +4108,7 @@
       </c>
       <c r="O49" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P49" t="n">
@@ -4183,7 +4183,7 @@
       </c>
       <c r="O50" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P50" t="n">
@@ -4258,7 +4258,7 @@
       </c>
       <c r="O51" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P51" t="n">
@@ -4333,7 +4333,7 @@
       </c>
       <c r="O52" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P52" t="n">
@@ -4408,7 +4408,7 @@
       </c>
       <c r="O53" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P53" t="n">
@@ -4483,7 +4483,7 @@
       </c>
       <c r="O54" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P54" t="n">
@@ -4558,7 +4558,7 @@
       </c>
       <c r="O55" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P55" t="n">
@@ -4633,7 +4633,7 @@
       </c>
       <c r="O56" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P56" t="n">
@@ -4708,7 +4708,7 @@
       </c>
       <c r="O57" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P57" t="n">
@@ -4783,7 +4783,7 @@
       </c>
       <c r="O58" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P58" t="n">
@@ -4858,7 +4858,7 @@
       </c>
       <c r="O59" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P59" t="n">
@@ -4933,7 +4933,7 @@
       </c>
       <c r="O60" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P60" t="n">
@@ -5008,7 +5008,7 @@
       </c>
       <c r="O61" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P61" t="n">
@@ -5083,7 +5083,7 @@
       </c>
       <c r="O62" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P62" t="n">
@@ -5158,7 +5158,7 @@
       </c>
       <c r="O63" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P63" t="n">
@@ -5233,7 +5233,7 @@
       </c>
       <c r="O64" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P64" t="n">
@@ -5308,7 +5308,7 @@
       </c>
       <c r="O65" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P65" t="n">
@@ -5383,7 +5383,7 @@
       </c>
       <c r="O66" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P66" t="n">
@@ -5458,7 +5458,7 @@
       </c>
       <c r="O67" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P67" t="n">
@@ -5533,7 +5533,7 @@
       </c>
       <c r="O68" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P68" t="n">
@@ -5608,7 +5608,7 @@
       </c>
       <c r="O69" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P69" t="n">
@@ -5683,7 +5683,7 @@
       </c>
       <c r="O70" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P70" t="n">
@@ -5758,7 +5758,7 @@
       </c>
       <c r="O71" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P71" t="n">
@@ -5790,11 +5790,11 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>CPM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D72" t="n">
-        <v>22291</v>
+        <v>22297</v>
       </c>
       <c r="E72" t="n">
         <v>647</v>
@@ -5833,7 +5833,7 @@
       </c>
       <c r="O72" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P72" t="n">
@@ -5908,7 +5908,7 @@
       </c>
       <c r="O73" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P73" t="n">
@@ -5983,7 +5983,7 @@
       </c>
       <c r="O74" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P74" t="n">
@@ -6058,7 +6058,7 @@
       </c>
       <c r="O75" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P75" t="n">
@@ -6133,7 +6133,7 @@
       </c>
       <c r="O76" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P76" t="n">
@@ -6208,7 +6208,7 @@
       </c>
       <c r="O77" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P77" t="n">
@@ -6283,7 +6283,7 @@
       </c>
       <c r="O78" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P78" t="n">
@@ -6358,7 +6358,7 @@
       </c>
       <c r="O79" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P79" t="n">
@@ -6433,7 +6433,7 @@
       </c>
       <c r="O80" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P80" t="n">
@@ -6508,7 +6508,7 @@
       </c>
       <c r="O81" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P81" t="n">
@@ -6583,7 +6583,7 @@
       </c>
       <c r="O82" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P82" t="n">
@@ -6658,7 +6658,7 @@
       </c>
       <c r="O83" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P83" t="n">
@@ -6733,7 +6733,7 @@
       </c>
       <c r="O84" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P84" t="n">
@@ -6808,7 +6808,7 @@
       </c>
       <c r="O85" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P85" t="n">
@@ -6883,7 +6883,7 @@
       </c>
       <c r="O86" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P86" t="n">
@@ -6958,7 +6958,7 @@
       </c>
       <c r="O87" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P87" t="n">
@@ -7033,7 +7033,7 @@
       </c>
       <c r="O88" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P88" t="n">
@@ -7108,7 +7108,7 @@
       </c>
       <c r="O89" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P89" t="n">
@@ -7183,7 +7183,7 @@
       </c>
       <c r="O90" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P90" t="n">
@@ -7258,7 +7258,7 @@
       </c>
       <c r="O91" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P91" t="n">
@@ -7333,7 +7333,7 @@
       </c>
       <c r="O92" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P92" t="n">
@@ -7408,7 +7408,7 @@
       </c>
       <c r="O93" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P93" t="n">
@@ -7483,7 +7483,7 @@
       </c>
       <c r="O94" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P94" t="n">
@@ -7558,7 +7558,7 @@
       </c>
       <c r="O95" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P95" t="n">
@@ -7633,7 +7633,7 @@
       </c>
       <c r="O96" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P96" t="n">
@@ -7708,7 +7708,7 @@
       </c>
       <c r="O97" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P97" t="n">
@@ -7783,7 +7783,7 @@
       </c>
       <c r="O98" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P98" t="n">
@@ -7858,7 +7858,7 @@
       </c>
       <c r="O99" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P99" t="n">
@@ -7933,7 +7933,7 @@
       </c>
       <c r="O100" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P100" t="n">
@@ -8008,7 +8008,7 @@
       </c>
       <c r="O101" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P101" t="n">
@@ -8083,7 +8083,7 @@
       </c>
       <c r="O102" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P102" t="n">
@@ -8158,7 +8158,7 @@
       </c>
       <c r="O103" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P103" t="n">
@@ -8233,7 +8233,7 @@
       </c>
       <c r="O104" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P104" t="n">
@@ -8308,7 +8308,7 @@
       </c>
       <c r="O105" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P105" t="n">
@@ -8383,7 +8383,7 @@
       </c>
       <c r="O106" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P106" t="n">
@@ -8458,7 +8458,7 @@
       </c>
       <c r="O107" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P107" t="n">
@@ -8533,7 +8533,7 @@
       </c>
       <c r="O108" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P108" t="n">
@@ -8608,7 +8608,7 @@
       </c>
       <c r="O109" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P109" t="n">
@@ -8683,7 +8683,7 @@
       </c>
       <c r="O110" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P110" t="n">
@@ -8758,7 +8758,7 @@
       </c>
       <c r="O111" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P111" t="n">
@@ -8833,7 +8833,7 @@
       </c>
       <c r="O112" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P112" t="n">
@@ -8908,7 +8908,7 @@
       </c>
       <c r="O113" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P113" t="n">
@@ -8983,7 +8983,7 @@
       </c>
       <c r="O114" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P114" t="n">
@@ -9058,7 +9058,7 @@
       </c>
       <c r="O115" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P115" t="n">
@@ -9133,7 +9133,7 @@
       </c>
       <c r="O116" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P116" t="n">
@@ -9208,7 +9208,7 @@
       </c>
       <c r="O117" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P117" t="n">
@@ -9283,7 +9283,7 @@
       </c>
       <c r="O118" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P118" t="n">
@@ -9358,7 +9358,7 @@
       </c>
       <c r="O119" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P119" t="n">
@@ -9433,7 +9433,7 @@
       </c>
       <c r="O120" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P120" t="n">
@@ -9508,7 +9508,7 @@
       </c>
       <c r="O121" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P121" t="n">
@@ -9583,7 +9583,7 @@
       </c>
       <c r="O122" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P122" t="n">
@@ -9658,7 +9658,7 @@
       </c>
       <c r="O123" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P123" t="n">
@@ -9733,7 +9733,7 @@
       </c>
       <c r="O124" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P124" t="n">
@@ -9808,7 +9808,7 @@
       </c>
       <c r="O125" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P125" t="n">
@@ -9883,7 +9883,7 @@
       </c>
       <c r="O126" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P126" t="n">
@@ -9958,7 +9958,7 @@
       </c>
       <c r="O127" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P127" t="n">
@@ -10033,7 +10033,7 @@
       </c>
       <c r="O128" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P128" t="n">
@@ -10108,7 +10108,7 @@
       </c>
       <c r="O129" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P129" t="n">
@@ -10183,7 +10183,7 @@
       </c>
       <c r="O130" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P130" t="n">
@@ -10258,7 +10258,7 @@
       </c>
       <c r="O131" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P131" t="n">
@@ -10333,7 +10333,7 @@
       </c>
       <c r="O132" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P132" t="n">
@@ -10408,7 +10408,7 @@
       </c>
       <c r="O133" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P133" t="n">
@@ -10483,7 +10483,7 @@
       </c>
       <c r="O134" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P134" t="n">
@@ -10558,7 +10558,7 @@
       </c>
       <c r="O135" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P135" t="n">
@@ -10633,7 +10633,7 @@
       </c>
       <c r="O136" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P136" t="n">
@@ -10708,7 +10708,7 @@
       </c>
       <c r="O137" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P137" t="n">
@@ -10783,7 +10783,7 @@
       </c>
       <c r="O138" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P138" t="n">
@@ -10858,7 +10858,7 @@
       </c>
       <c r="O139" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P139" t="n">
@@ -10933,7 +10933,7 @@
       </c>
       <c r="O140" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P140" t="n">
@@ -11008,7 +11008,7 @@
       </c>
       <c r="O141" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P141" t="n">
@@ -11083,7 +11083,7 @@
       </c>
       <c r="O142" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P142" t="n">
@@ -11158,7 +11158,7 @@
       </c>
       <c r="O143" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P143" t="n">
@@ -11233,7 +11233,7 @@
       </c>
       <c r="O144" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P144" t="n">
@@ -11308,7 +11308,7 @@
       </c>
       <c r="O145" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P145" t="n">
@@ -11383,7 +11383,7 @@
       </c>
       <c r="O146" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P146" t="n">
@@ -11458,7 +11458,7 @@
       </c>
       <c r="O147" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P147" t="n">
@@ -11533,7 +11533,7 @@
       </c>
       <c r="O148" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P148" t="n">
@@ -11608,7 +11608,7 @@
       </c>
       <c r="O149" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P149" t="n">
@@ -11683,7 +11683,7 @@
       </c>
       <c r="O150" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P150" t="n">
@@ -11758,7 +11758,7 @@
       </c>
       <c r="O151" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P151" t="n">
@@ -11833,7 +11833,7 @@
       </c>
       <c r="O152" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P152" t="n">
@@ -11908,7 +11908,7 @@
       </c>
       <c r="O153" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P153" t="n">
@@ -11983,7 +11983,7 @@
       </c>
       <c r="O154" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P154" t="n">
@@ -12058,7 +12058,7 @@
       </c>
       <c r="O155" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P155" t="n">
@@ -12133,7 +12133,7 @@
       </c>
       <c r="O156" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P156" t="n">
@@ -12208,7 +12208,7 @@
       </c>
       <c r="O157" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P157" t="n">
@@ -12283,7 +12283,7 @@
       </c>
       <c r="O158" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P158" t="n">
@@ -12358,7 +12358,7 @@
       </c>
       <c r="O159" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P159" t="n">
@@ -12433,7 +12433,7 @@
       </c>
       <c r="O160" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P160" t="n">
@@ -12508,7 +12508,7 @@
       </c>
       <c r="O161" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>FEMALE</t>
         </is>
       </c>
       <c r="P161" t="n">
@@ -12583,7 +12583,7 @@
       </c>
       <c r="O162" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P162" t="n">
@@ -12658,7 +12658,7 @@
       </c>
       <c r="O163" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P163" t="n">
@@ -12733,7 +12733,7 @@
       </c>
       <c r="O164" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P164" t="n">
@@ -12808,7 +12808,7 @@
       </c>
       <c r="O165" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P165" t="n">
@@ -12883,7 +12883,7 @@
       </c>
       <c r="O166" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P166" t="n">
@@ -12958,7 +12958,7 @@
       </c>
       <c r="O167" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P167" t="n">
@@ -13033,7 +13033,7 @@
       </c>
       <c r="O168" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P168" t="n">
@@ -13108,7 +13108,7 @@
       </c>
       <c r="O169" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P169" t="n">
@@ -13183,7 +13183,7 @@
       </c>
       <c r="O170" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P170" t="n">
@@ -13258,7 +13258,7 @@
       </c>
       <c r="O171" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>FEMALE</t>
         </is>
       </c>
       <c r="P171" t="n">
@@ -13333,7 +13333,7 @@
       </c>
       <c r="O172" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P172" t="n">
@@ -13408,7 +13408,7 @@
       </c>
       <c r="O173" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P173" t="n">
@@ -13483,7 +13483,7 @@
       </c>
       <c r="O174" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P174" t="n">
@@ -13558,7 +13558,7 @@
       </c>
       <c r="O175" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P175" t="n">
@@ -13633,7 +13633,7 @@
       </c>
       <c r="O176" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P176" t="n">
@@ -13665,11 +13665,11 @@
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>CPM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D177" t="n">
-        <v>22291</v>
+        <v>22297</v>
       </c>
       <c r="E177" t="n">
         <v>7193</v>
@@ -13708,7 +13708,7 @@
       </c>
       <c r="O177" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P177" t="n">
@@ -13783,7 +13783,7 @@
       </c>
       <c r="O178" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P178" t="n">
@@ -13858,7 +13858,7 @@
       </c>
       <c r="O179" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P179" t="n">
@@ -13933,7 +13933,7 @@
       </c>
       <c r="O180" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P180" t="n">
@@ -14008,7 +14008,7 @@
       </c>
       <c r="O181" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P181" t="n">
@@ -14083,7 +14083,7 @@
       </c>
       <c r="O182" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P182" t="n">
@@ -14158,7 +14158,7 @@
       </c>
       <c r="O183" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P183" t="n">
@@ -14233,7 +14233,7 @@
       </c>
       <c r="O184" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P184" t="n">
@@ -14308,7 +14308,7 @@
       </c>
       <c r="O185" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P185" t="n">
@@ -14383,7 +14383,7 @@
       </c>
       <c r="O186" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P186" t="n">
@@ -14406,11 +14406,11 @@
     </row>
     <row r="187">
       <c r="A187" t="n">
-        <v>1730838</v>
+        <v>1730837</v>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>Malladi Udhayalakshmi</t>
+          <t>Dhulipudi Madhava Venkanna</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
@@ -14443,7 +14443,7 @@
       </c>
       <c r="K187" t="inlineStr">
         <is>
-          <t>Malladi Udhayalakshmi</t>
+          <t>Dhulipudi Madhava Venkanna</t>
         </is>
       </c>
       <c r="L187" t="inlineStr">
@@ -14458,11 +14458,11 @@
       </c>
       <c r="O187" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P187" t="n">
-        <v>43</v>
+        <v>34</v>
       </c>
       <c r="Q187" t="b">
         <v>0</v>
@@ -14481,11 +14481,11 @@
     </row>
     <row r="188">
       <c r="A188" t="n">
-        <v>1730837</v>
+        <v>1730838</v>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>Dhulipudi Madhava Venkanna</t>
+          <t>Malladi Udhayalakshmi</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
@@ -14518,7 +14518,7 @@
       </c>
       <c r="K188" t="inlineStr">
         <is>
-          <t>Dhulipudi Madhava Venkanna</t>
+          <t>Malladi Udhayalakshmi</t>
         </is>
       </c>
       <c r="L188" t="inlineStr">
@@ -14533,11 +14533,11 @@
       </c>
       <c r="O188" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>FEMALE</t>
         </is>
       </c>
       <c r="P188" t="n">
-        <v>34</v>
+        <v>43</v>
       </c>
       <c r="Q188" t="b">
         <v>0</v>
